--- a/testcase/测试用例.xlsx
+++ b/testcase/测试用例.xlsx
@@ -423,15 +423,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="39" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -469,759 +469,576 @@
     <row r="2" ht="25" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>商品添加与数量修改</t>
+          <t>MAC平台</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>正向-点击添加按钮成功增加商品数量并同步更新金额</t>
+          <t>MAC平台使用内嵌商品平台功能-正常操作</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>用户已登录，商品详情页打开，商品库存充足（如库存≥5），当前数量为1</t>
+          <t>MAC设备，系统为macOS，安装Chrome浏览器，网络正常</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1. 在商品详情页找到数量选择区域
-2. 点击“+”添加按钮一次
-3. 观察数量显示及总金额变化</t>
+          <t>1. 打开Chrome浏览器，访问商品平台页面；2. 点击内嵌商品功能按钮；3. 浏览商品详情、添加购物车</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>数量从1变为2，商品单价不变，总金额=单价*2，页面实时更新</t>
+          <t>商品平台正常加载，内嵌功能如查看、购买、搜索均正常响应，界面无错乱</t>
         </is>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>商品添加与数量修改</t>
+          <t>MAC平台</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>反向-数量超过库存时添加按钮禁用并提示库存不足</t>
+          <t>MAC平台使用内嵌商品平台功能-多窗口切换</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>用户已登录，商品详情页打开，商品当前数量已等于库存（如库存=3，当前数量=3）</t>
+          <t>MAC设备，系统为macOS，打开商品平台内嵌页面，另开一个应用窗口</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1. 在商品详情页找到数量选择区域
-2. 尝试点击“+”添加按钮
-3. 观察按钮状态及页面提示</t>
+          <t>1. 在内嵌商品平台进行商品浏览；2. 切换至其他应用窗口；3. 切回浏览器窗口</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>“+”按钮变为灰色不可点击，页面出现提示“库存不足”或“已达最大可购数量”，总金额不变</t>
+          <t>内嵌商品平台状态保持正常，未出现白屏或功能异常</t>
         </is>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>商品删除操作</t>
+          <t>WIN平台</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>正向-点击删除按钮成功移除商品并更新总金额</t>
+          <t>WIN平台使用内嵌商品平台功能-标准操作</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>购物车中存在至少2件商品，用户已登录</t>
+          <t>Windows设备，系统为Win10/11，安装Edge浏览器，网络正常</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1. 进入购物车页面
-2. 点击目标商品所在行的“删除”按钮
-3. 确认删除弹出框点击“确定”
-4. 观察购物车列表及底部总金额</t>
+          <t>1. 打开Edge浏览器，访问商品平台；2. 激活内嵌功能，选择商品分类；3. 完成下单流程</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>该商品从购物车列表中移除，总金额扣除该商品金额，并正确显示剩余商品总价</t>
+          <t>内嵌商品平台流畅运行，弹出窗口、滚动、点击均正常</t>
         </is>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>商品删除操作</t>
+          <t>WIN平台</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>反向-删除最后一件商品时确认提示后正常删除</t>
+          <t>WIN平台使用内嵌商品平台功能-缩放测试</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>购物车中仅有1件商品，用户已登录</t>
+          <t>Windows设备，浏览器缩放到150%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1. 进入购物车页面
-2. 点击唯一商品所在行的“删除”按钮
-3. 观察弹出的确认提示框内容
-4. 点击提示框中的“确定”
-5. 观察购物车页面状态</t>
+          <t>1. 打开内嵌商品平台；2. 调整浏览器缩放至80%和150%；3. 检查布局和可操作按钮</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>确认提示框内容明确提示“是否删除最后一件商品”，删除后购物车显示为空状态，总金额变为0</t>
+          <t>页面按比例自适应，无元素重叠或隐藏，按钮可点击</t>
         </is>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>地址选择与新增</t>
+          <t>google</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>正向-从已有地址列表中选择一个地址并自动填充</t>
+          <t>Chrome浏览器使用内嵌商品平台功能-基本功能</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>用户已登录，已添加至少2个有效地址，订单确认页已打开</t>
+          <t>安装Chrome最新版，网络正常</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1. 在订单确认页找到收货地址区域
-2. 点击地址下拉选择框或地址列表
-3. 选择一个非当前默认的地址
-4. 观察页面地址信息变化</t>
+          <t>1. 用Chrome打开商品平台网页；2. 点击“内嵌商品平台”入口；3. 使用搜索、筛选、购买功能</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>所选地址的详细（收件人、电话、地址）自动显示在对应区域，且与选中的地址一致</t>
+          <t>内嵌页面加载成功，响应迅速，所有操作无报错</t>
         </is>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>地址选择与新增</t>
+          <t>google</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>反向-未选择地址时提交订单提示请选择收货地址</t>
+          <t>Chrome浏览器使用内嵌商品平台功能-无痕模式</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>用户已登录，订单确认页打开，但收件地址区域为空（无默认地址）</t>
+          <t>打开Chrome无痕窗口</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1. 确保地址列表未选中任何地址
-2. 直接点击“提交订单”按钮
-3. 观察页面响应</t>
+          <t>1. 在无痕模式下访问商品平台；2. 使用内嵌功能进行商品浏览</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>提交失败，页面弹出提示“请选择收货地址”或红色高亮提示地址必填，订单未生成</t>
+          <t>内嵌商品平台功能正常，无提示“需登录”或功能受限（除非业务要求）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>地址信息校验</t>
+          <t>firefox</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>正向-新增地址填写完整信息后成功保存</t>
+          <t>Firefox使用内嵌商品平台功能-兼容性测试</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>用户已登录，进入地址管理页，点击“新增地址”</t>
+          <t>安装Firefox最新版，网络正常</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1. 输入收件人姓名：张三
-2. 输入手机号：13800138000
-3. 选择所在省/市/区：广东省-深圳市-南山区
-4. 输入详细地址：科技园路1号
-5. 点击“保存”按钮</t>
+          <t>1. 用Firefox打开商品平台；2. 激活内嵌功能，执行添加收藏、加入购物车；3. 查看购物车图标更新</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>提示“地址保存成功”，新地址出现在地址列表中，且信息完整正确</t>
+          <t>内嵌商品平台在所有核心操作上表现与Chrome一致，无CSS兼容性问题</t>
         </is>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>地址信息校验</t>
+          <t>firefox</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>反向-电话格式错误时保存失败并提示电话格式</t>
+          <t>Firefox使用内嵌商品平台功能-页面滚动性能</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>用户已登录，进入地址管理页，点击“新增地址”</t>
+          <t>Firefox浏览器，加载大量商品列表的内嵌页面</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1. 输入收件人姓名：李四
-2. 输入手机号：12345（位数不足或格式错误）
-3. 填写其他必填项都正确
-4. 点击“保存”按钮</t>
+          <t>1. 快速上下滚动商品列表；2. 点击“加载更多”按钮</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>保存失败，手机号输入框下方或页面提示“请输入正确的手机号格式”，地址列表未新增</t>
+          <t>滚动流畅无卡顿，加载更多后无布局混乱</t>
         </is>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>优惠券领取与使用</t>
+          <t>EDGE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>正向-选择可用优惠券后订单金额正确减免</t>
+          <t>Edge使用内嵌商品平台功能-基本操作</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>用户已登录，购物车中有商品，总价为100元，用户有1张满100减10元的可用优惠券</t>
+          <t>安装Edge最新版，网络正常</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1. 进入订单确认页
-2. 在优惠券/优惠码区域点击“选择优惠券”
-3. 从列表中选择该张可用优惠券
-4. 观察订单金额变化</t>
+          <t>1. 用Edge打开商品平台；2. 使用内嵌功能浏览商品，点击商品图片；3. 切换至详情页</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>订单总金额从100元更新为90元（优惠10元），优惠券信息显示已使用</t>
+          <t>商品图片放大、描述显示正常，后退按钮有效</t>
         </is>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>优惠券领取与使用</t>
+          <t>EDGE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>反向-使用过期或未达门槛优惠券则不可选</t>
+          <t>Edge使用内嵌商品平台功能-多标签页</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>用户已登录，订单确认页面，购物车总价50元，用户有1张满100减20的优惠券（已过期或未达门槛）</t>
+          <t>Edge浏览器，已打开多个标签页</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1. 进入订单确认页面优惠券选择区域
-2. 展开可用优惠券列表
-3. 查看该张优惠券的状态</t>
+          <t>1. 在内嵌商品平台的标签页进行操作；2. 切换到其他标签页再切回</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>该张优惠券显示为灰色不可选择，并标注“未满足使用条件”或“已过期”，无法选中，订单金额不变</t>
+          <t>内嵌页面保持会话，未自动刷新或丢失数据</t>
         </is>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>满减活动校验</t>
+          <t>4g</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>正向-订单金额满足满减条件时自动应用优惠</t>
+          <t>4G网络环境使用内嵌商品平台功能-加载性能</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>平台有满200减20活动，用户购物车商品总金额为220元，用户已登录</t>
+          <t>手机开启4G网络（限速模拟），打开测试网页</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1. 进入订单确认页面
-2. 查看订单金额汇总区域
-3. 系统自动计算满减</t>
+          <t>1. 访问商品平台内嵌页面；2. 记录页面加载时间；3. 进行商品搜索和购买</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>活动自动应用，订单总金额显示为200元（220-20），且有明细展示活动优惠</t>
+          <t>页面加载在可接受时间（如5秒内），基本功能可用，无超时中断</t>
         </is>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>满减活动校验</t>
+          <t>4g</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>反向-删除商品后订单金额不满足满减则取消优惠</t>
+          <t>4G网络环境使用内嵌商品平台功能-弱信号</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>平台有满200减20活动，购物车商品总价为210元，用户已登录进入订单确认页，已自动应用满减优惠</t>
+          <t>4G信号降至1格（物理或工具模拟）</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1. 返回购物车页面
-2. 删除一件商品，使总价降至190元
-3. 再次进入订单确认页面
-4. 观察金额及优惠状态</t>
+          <t>1. 打开内嵌商品平台；2. 点选商品；3. 观察加载状态和错误提示</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>订单金额为190元，满减优惠自动失效，没有20元减免，总金额恢复为190元</t>
+          <t>页面给出合理的加载中提示，超时后显示“网络异常”，不崩溃</t>
         </is>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>提交订单操作</t>
+          <t>网络异常</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>正向-所有必填项完整后点击提交订单成功生成订单</t>
+          <t>网络异常环境使用内嵌商品平台功能-断网测试</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>用户已登录，订单确认页面已选择收货地址、填写备注，使用默认支付方式，库存充足</t>
+          <t>设备已连接网络，然后手动断开网络连接</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1. 确认地址、商品、金额等所有信息无误
-2. 点击“提交订单”按钮
-3. 观察页面跳转</t>
+          <t>1. 在已加载的内嵌商品平台页面上点击商品链接；2. 观察页面行为</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>提交成功，页面跳转至支付页面或订单成功页面，系统生成一个订单编号，状态为“待支付”</t>
+          <t>出现断网提示（如“无网络连接”），原有页面元素保持，提供重试按钮</t>
         </is>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>提交订单操作</t>
+          <t>网络异常</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>反向-库存不足时提交订单失败并提示库存不足</t>
+          <t>网络异常环境使用内嵌商品平台功能-高延迟</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>用户已登录，购物车中有商品A，但A库存仅剩1件且已被其他用户锁定或下单，实际库存不足</t>
+          <t>使用网络延迟工具（如Fiddler）模拟高延迟（&gt;2000ms）</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1. 确认所有信息填写完整
-2. 点击“提交订单”按钮
-3. 观察页面反馈</t>
+          <t>1. 访问内嵌商品平台页面；2. 进行添加购物车操作</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>提交失败，页面弹出提示“商品A库存不足”或“库存不够，请修改数量”，订单未生成</t>
+          <t>操作按钮显示加载状态，超时后给出反馈（如“操作超时，请重试”），无界面冻结</t>
         </is>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>支付流程处理</t>
+          <t>移动端样式</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>正向-选择支付方式后跳转支付页面并支付成功</t>
+          <t>移动设备使用内嵌商品平台功能-响应式布局</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>用户已登录，订单已生成且处于“待支付”状态，支付页面支持余额支付</t>
+          <t>手机设备（iPhone 14/Android典型机型），竖屏模式</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1. 在支付页面选择支付方式（如余额支付）
-2. 点击“立即支付”
-3. 在后续支付确认页点击“确认支付”
-4. 观察状态</t>
+          <t>1. 使用手机浏览器访问商品平台内嵌页面；2. 上下滑动浏览商品；3. 点击商品按钮</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>跳转至支付成功页面，用户余额相应扣减，订单状态变为“已支付”或“待发货”</t>
+          <t>页面自适应移动屏幕宽度，按钮大小适合触屏，无水平滚动条</t>
         </is>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>支付流程处理</t>
+          <t>移动端样式</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>反向-支付超时或取消支付则订单保持待支付状态</t>
+          <t>移动设备使用内嵌商品平台功能-横屏适配</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>用户已登录，订单已生成处于“待支付”状态</t>
+          <t>手机设备，旋转为横屏</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1. 选择支付方式后点击“立即支付”
-2. 在支付页面等待超时（如倒计时结束）或点击“取消支付”
-3. 返回订单列表查看订单状态</t>
+          <t>1. 在内嵌商品平台横屏模式下浏览；2. 旋转回竖屏</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>订单未被支付成功，状态仍为“待支付”，用户可在有效期内再次支付，或超时后订单自动取消</t>
+          <t>布局根据屏幕方向自动调整，内容不丢失，功能正常</t>
         </is>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>规格选项切换</t>
+          <t>平板样式</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>正向-选择不同规格后价格和图片更新</t>
+          <t>平板用户使用内嵌商品平台功能-分屏模式</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>用户已登录，商品有多个规格（如颜色：黑/白，尺寸：S/M/L），商品详情页打开，默认选中一种规格</t>
+          <t>iPad或Android平板，系统支持分屏，网络正常</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1. 点击“颜色”规格中的“白色”选项
-2. 观察商品主图片是否切换为白色款
-3. 查看价格是否变化（若不同规格价格不同）
-4. 再点击“尺寸”中的“L”选项</t>
+          <t>1. 开启分屏，左侧打开内嵌商品平台；2. 右侧打开其他应用；3. 操作商品平台</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>商品主图片更新为对应款式，价格如不同则同步更新，所选规格标签高亮</t>
+          <t>内嵌商品平台在分屏下布局正常，按钮可点击，无内容截断</t>
         </is>
       </c>
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>规格选项切换</t>
+          <t>平板样式</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>反向-所选规格库存为零时提示无货并无法添加</t>
+          <t>平板用户使用内嵌商品平台功能-大屏适配</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>用户已登录，商品某规格（如颜色：蓝色，尺寸：L）库存为0</t>
+          <t>平板横屏使用，分辨率2560x1600</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1. 在商品详情页点击该库存为0的规格组合
-2. 观察“加入购物车”或“立即购买”按钮状态
-3. 尝试点击按钮</t>
+          <t>1. 访问商品平台内嵌页面；2. 查看商品列表网格布局；3. 点击商品详情</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>该规格组合显示“已售罄”或“无货”，购买按钮置灰不可点击，用户无法添加至购物车</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="25" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>数量输入校验</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>正向-手动输入合理数量后金额同步更新</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>用户已登录，商品详情页打开，商品单价明确，库存≥10</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1. 找到数量输入框
-2. 清空默认值，输入数字“5”
-3. 按回车或点击页面其他区域</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>数量变为5，总金额显示为单价*5，并实时更新</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="25" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>数量输入校验</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>反向-输入非数字或负数时阻止输入或重置为1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>用户已登录，商品详情页打开</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1. 在数量输入框中输入“-2”
-2. 或者输入“abc”
-3. 按回车或失去焦点</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>输入框阻止无效输入，或自动重置为合理最小值（如1），并给出提示“请输入有效数量”</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>备注信息填写</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>正向-在备注框输入合理文字后提交订单保留备注</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>用户已登录，订单确认页打开，备注输入框可见</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>1. 在备注输入框中输入“请轻放，防水包装”
-2. 点击“提交订单”
-3. 在订单详情页查看备注信息</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>提交后订单成功生成，在订单详情页中“备注”字段显示“请轻放，防水包装”</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="25" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>备注信息填写</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>反向-备注输入超长字符时截断或提示超出限制</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>用户已登录，订单确认页打开，备注输入框有字符上限（如200字）</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1. 在备注输入框中输入超过200字的内容（复制长文本）
-2. 失去焦点或尝试提交订单
-3. 观察输入框反应</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>输入框无法输入超出部分，或提交时提示“备注内容超过200字限制”，且内容被截断至200字，不影响订单提交</t>
+          <t>商品展示充分利用屏幕空间，间距合理，无空白过多或元素挤压</t>
         </is>
       </c>
     </row>

--- a/testcase/测试用例.xlsx
+++ b/testcase/测试用例.xlsx
@@ -423,15 +423,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="39" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -469,231 +469,241 @@
     <row r="2" ht="25" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MAC平台</t>
+          <t>Z轴升降准确性</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MAC平台使用内嵌商品平台功能-正常操作</t>
+          <t>正向-Z轴升降至指定高度位置精度准确</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MAC设备，系统为macOS，安装Chrome浏览器，网络正常</t>
+          <t>打印机已开机并完成归零，Z轴无负载</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1. 打开Chrome浏览器，访问商品平台页面；2. 点击内嵌商品功能按钮；3. 浏览商品详情、添加购物车</t>
+          <t>1. 在控制界面输入目标高度值（例如50mm）
+2. 点击“Z轴移动”按钮
+3. 使用卡尺测量实际升降高度</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>商品平台正常加载，内嵌功能如查看、购买、搜索均正常响应，界面无错乱</t>
+          <t>实际升降高度与设定值误差在±0.1mm以内</t>
         </is>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MAC平台</t>
+          <t>Z轴升降准确性</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MAC平台使用内嵌商品平台功能-多窗口切换</t>
+          <t>反向-Z轴升降超过限位时触发保护</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MAC设备，系统为macOS，打开商品平台内嵌页面，另开一个应用窗口</t>
+          <t>Z轴位于行程中间位置</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1. 在内嵌商品平台进行商品浏览；2. 切换至其他应用窗口；3. 切回浏览器窗口</t>
+          <t>1. 连续发送向上移动指令直至超过顶部限位
+2. 连续发送向下移动指令直至超过底部限位</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>内嵌商品平台状态保持正常，未出现白屏或功能异常</t>
+          <t>当Z轴触碰限位开关时，电机立即停止，屏幕显示“行程超限”报警</t>
         </is>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WIN平台</t>
+          <t>Z轴运动平稳性</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WIN平台使用内嵌商品平台功能-标准操作</t>
+          <t>正向-Z轴升降过程无明显抖动卡顿</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Windows设备，系统为Win10/11，安装Edge浏览器，网络正常</t>
+          <t>打印机放置在水平稳定平台，Z轴空载</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1. 打开Edge浏览器，访问商品平台；2. 激活内嵌功能，选择商品分类；3. 完成下单流程</t>
+          <t>1. 设置Z轴以10mm/s速度匀速升降
+2. 全程观察并录制视频
+3. 在升降过程中触碰Z轴导杆</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>内嵌商品平台流畅运行，弹出窗口、滚动、点击均正常</t>
+          <t>Z轴运动连续无可见抖动、卡顿或异响，触碰时无明显位移突变</t>
         </is>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WIN平台</t>
+          <t>Z轴运动平稳性</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WIN平台使用内嵌商品平台功能-缩放测试</t>
+          <t>反向-Z轴负载过重时报警提示</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Windows设备，浏览器缩放到150%</t>
+          <t>Z轴处于空载状态，准备额外砝码（超过额定负载150%）</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1. 打开内嵌商品平台；2. 调整浏览器缩放至80%和150%；3. 检查布局和可操作按钮</t>
+          <t>1. 在Z轴平台上放置超负载砝码
+2. 发送向上移动指令</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>页面按比例自适应，无元素重叠或隐藏，按钮可点击</t>
+          <t>Z轴无法启动或启动2秒内停止，屏幕显示“负载超重，请减轻重量”</t>
         </is>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>加热至设定温度</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chrome浏览器使用内嵌商品平台功能-基本功能</t>
+          <t>正向-启动加热后树脂槽温度达标</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>安装Chrome最新版，网络正常</t>
+          <t>树脂槽空且清洁，环境温度25℃，加热功能开启</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1. 用Chrome打开商品平台网页；2. 点击“内嵌商品平台”入口；3. 使用搜索、筛选、购买功能</t>
+          <t>1. 在控制界面设置目标温度35℃
+2. 点击“开始加热”
+3. 等待并记录实际温度升至35℃的时间</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>内嵌页面加载成功，响应迅速，所有操作无报错</t>
+          <t>加热系统在5分钟内将树脂槽温度升至35℃±1℃，并停止加热</t>
         </is>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>加热至设定温度</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chrome浏览器使用内嵌商品平台功能-无痕模式</t>
+          <t>反向-加热超过安全温度自动断电</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>打开Chrome无痕窗口</t>
+          <t>打印机内部温度传感器正常，加热器工作正常</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1. 在无痕模式下访问商品平台；2. 使用内嵌功能进行商品浏览</t>
+          <t>1. 通过后台参数将加热目标温度设置为60℃（超过安全阈值）
+2. 开始加热并监控温度</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>内嵌商品平台功能正常，无提示“需登录”或功能受限（除非业务要求）</t>
+          <t>当温度达到55℃时，系统自动切断加热电源，并在屏幕显示“超温保护触发”</t>
         </is>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>firefox</t>
+          <t>恒温保持稳定性</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Firefox使用内嵌商品平台功能-兼容性测试</t>
+          <t>正向-温度到达后波动在合理范围</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>安装Firefox最新版，网络正常</t>
+          <t>树脂槽温度已稳定在35℃，树脂槽内装有常用树脂</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1. 用Firefox打开商品平台；2. 激活内嵌功能，执行添加收藏、加入购物车；3. 查看购物车图标更新</t>
+          <t>1. 持续记录温度10分钟，每30秒采样一次
+2. 计算温度波动范围</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>内嵌商品平台在所有核心操作上表现与Chrome一致，无CSS兼容性问题</t>
+          <t>所有采样点温度在35℃±2℃之间，无明显持续上升或下降趋势</t>
         </is>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>firefox</t>
+          <t>恒温保持稳定性</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -703,125 +713,133 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Firefox使用内嵌商品平台功能-页面滚动性能</t>
+          <t>反向-加热传感器失效时显示故障</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Firefox浏览器，加载大量商品列表的内嵌页面</t>
+          <t>准备一个已断线的加热传感器连接到主板</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1. 快速上下滚动商品列表；2. 点击“加载更多”按钮</t>
+          <t>1. 更换为断线传感器
+2. 启动加热功能
+3. 观察屏幕</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>滚动流畅无卡顿，加载更多后无布局混乱</t>
+          <t>2秒内屏幕显示“加热传感器故障，请检查”且加热不启动</t>
         </is>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EDGE</t>
+          <t>曝光时间设置与执行</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Edge使用内嵌商品平台功能-基本操作</t>
+          <t>正向-设置曝光时间后层固化时间匹配</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>安装Edge最新版，网络正常</t>
+          <t>切片文件已导入，设定层数为10层，每层曝光时间8秒</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1. 用Edge打开商品平台；2. 使用内嵌功能浏览商品，点击商品图片；3. 切换至详情页</t>
+          <t>1. 开始打印
+2. 使用秒表测量第一层曝光时长
+3. 记录每层实际曝光时间</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>商品图片放大、描述显示正常，后退按钮有效</t>
+          <t>每层实际曝光时间均为8秒±0.2秒，总耗时符合8秒×层数</t>
         </is>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EDGE</t>
+          <t>曝光时间设置与执行</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Edge使用内嵌商品平台功能-多标签页</t>
+          <t>反向-曝光时间设为0时触发提醒</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Edge浏览器，已打开多个标签页</t>
+          <t>打印机处于待机状态，尚未开始打印</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1. 在内嵌商品平台的标签页进行操作；2. 切换到其他标签页再切回</t>
+          <t>1. 在参数设置中将曝光时间改为0
+2. 点击“保存应用”
+3. 尝试开始打印</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>内嵌页面保持会话，未自动刷新或丢失数据</t>
+          <t>弹出提示框：“曝光时间不能为0，请设置有效值(&gt;0秒)”且打印无法启动</t>
         </is>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4g</t>
+          <t>曝光均匀性</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4G网络环境使用内嵌商品平台功能-加载性能</t>
+          <t>正向-整幅画面曝光亮度均匀</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>手机开启4G网络（限速模拟），打开测试网页</t>
+          <t>打印机光源已预热5分钟，使用照度计，投影区域无遮挡</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1. 访问商品平台内嵌页面；2. 记录页面加载时间；3. 进行商品搜索和购买</t>
+          <t>1. 运行投影全幅白色画面
+2. 在投影区域均匀选取9个点（3×3网格）测量照度
+3. 记录各点照度值</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>页面加载在可接受时间（如5秒内），基本功能可用，无超时中断</t>
+          <t>9个点照度最大值与最小值的差异≤10%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4g</t>
+          <t>曝光均匀性</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -831,29 +849,31 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4G网络环境使用内嵌商品平台功能-弱信号</t>
+          <t>反向-部分区域曝光不足导致固化失败</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4G信号降至1格（物理或工具模拟）</t>
+          <t>将树脂槽局部用遮光膜覆盖（模拟光学故障）</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1. 打开内嵌商品平台；2. 点选商品；3. 观察加载状态和错误提示</t>
+          <t>1. 放置遮光膜覆盖投影区域左下角1/4
+2. 开始打印标准测试件（面积覆盖整幅投影）
+3. 取出固化后模型</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>页面给出合理的加载中提示，超时后显示“网络异常”，不崩溃</t>
+          <t>被遮挡区域模型未固化或固化层厚度不足0.1mm，其余区域固化正常</t>
         </is>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>网络异常</t>
+          <t>延时启动打印</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -863,61 +883,65 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>网络异常环境使用内嵌商品平台功能-断网测试</t>
+          <t>正向-设定延时后按时自动开始打印</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>设备已连接网络，然后手动断开网络连接</t>
+          <t>打印机时间与手机/网络时间同步，树脂槽已准备就绪，文件已加载</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1. 在已加载的内嵌商品平台页面上点击商品链接；2. 观察页面行为</t>
+          <t>1. 设置延时打印：12小时后开始
+2. 打印机进入待机状态
+3. 等待12小时并观察</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>出现断网提示（如“无网络连接”），原有页面元素保持，提供重试按钮</t>
+          <t>12小时后打印机自动启动打印，与正常启动打印行为一致</t>
         </is>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>网络异常</t>
+          <t>延时启动打印</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>网络异常环境使用内嵌商品平台功能-高延迟</t>
+          <t>反向-延时期间断电后任务丢失</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>使用网络延迟工具（如Fiddler）模拟高延迟（&gt;2000ms）</t>
+          <t>已设定延时打印任务（剩余2小时），打印机处于待机状态</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1. 访问内嵌商品平台页面；2. 进行添加购物车操作</t>
+          <t>1. 切断打印机电源
+2. 等待5分钟
+3. 重新接通电源并开机</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>操作按钮显示加载状态，超时后给出反馈（如“操作超时，请重试”），无界面冻结</t>
+          <t>开机后延时任务消失，无自动启动，需重新设置延时打印</t>
         </is>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>移动端样式</t>
+          <t>延时参数修改</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -927,29 +951,31 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>移动设备使用内嵌商品平台功能-响应式布局</t>
+          <t>正向-延时过程中可更改剩余时间</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>手机设备（iPhone 14/Android典型机型），竖屏模式</t>
+          <t>已设置延时打印，剩余时间3小时，打印尚未开始</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1. 使用手机浏览器访问商品平台内嵌页面；2. 上下滑动浏览商品；3. 点击商品按钮</t>
+          <t>1. 进入延时设置界面
+2. 将剩余时间修改为1小时
+3. 确认保存</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>页面自适应移动屏幕宽度，按钮大小适合触屏，无水平滚动条</t>
+          <t>显示屏更新为剩余1小时，打印机将在1小时后启动打印</t>
         </is>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>移动端样式</t>
+          <t>延时参数修改</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -959,86 +985,570 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>移动设备使用内嵌商品平台功能-横屏适配</t>
+          <t>反向-打印开始后无法修改延时</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>手机设备，旋转为横屏</t>
+          <t>打印正在进行中，已打印3层</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1. 在内嵌商品平台横屏模式下浏览；2. 旋转回竖屏</t>
+          <t>1. 尝试进入延时设置界面
+2. 尝试修改延时参数</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>布局根据屏幕方向自动调整，内容不丢失，功能正常</t>
+          <t>延时设置界面不可进入或相关参数灰显，无法修改；屏幕提示“打印中不可修改延时”</t>
         </is>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>平板样式</t>
+          <t>手动中断后续打</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>平板用户使用内嵌商品平台功能-分屏模式</t>
+          <t>正向-暂停后继续打印层间无错位</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>iPad或Android平板，系统支持分屏，网络正常</t>
+          <t>打印已进行到第5层，打印机稳定运行</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1. 开启分屏，左侧打开内嵌商品平台；2. 右侧打开其他应用；3. 操作商品平台</t>
+          <t>1. 点击“暂停”按钮
+2. 等待30秒
+3. 点击“继续打印”
+4. 打印完成后取出模型，检查第5层与第6层接合处</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>内嵌商品平台在分屏下布局正常，按钮可点击，无内容截断</t>
+          <t>第5层与第6层之间无明显错位（≤0.05mm），模型整体外观正常</t>
         </is>
       </c>
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>平板样式</t>
+          <t>手动中断后续打</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>反向-断电后续打需重新校准</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>打印进行到第10层时突然断电</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1. 恢复供电并开机
+2. 选择续打功能
+3. 观察续打过程与成品</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>打印机提示需重新校准平台水平，校准后方可续打；续打后第10层与第11层可能有轻微错位（≤0.2mm）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="25" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>自动中断续打</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>正向-料耗尽加料后自动续打</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>树脂槽内树脂量仅够打印3层（当前第2层），配有料位传感器</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1. 开始打印
+2. 当打印到第4层时料位报警
+3. 手动加入足量树脂
+4. 观察打印机行为</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>加入树脂后，打印机自动暂停的打印任务在60秒内恢复，层间无错位（≤0.05mm）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>自动中断续打</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>平板用户使用内嵌商品平台功能-大屏适配</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>平板横屏使用，分辨率2560x1600</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1. 访问商品平台内嵌页面；2. 查看商品列表网格布局；3. 点击商品详情</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>商品展示充分利用屏幕空间，间距合理，无空白过多或元素挤压</t>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>反向-连续中断多次导致模型报废</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>使用易脆树脂，打印复杂镂空模型（第6层）</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1. 在打印过程中强制断电/断料5次
+2. 每次中断后恢复续打
+3. 打印完成后取出模型</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>模型层间出现明显错位、分层或断裂，模型报废无法使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>树脂参数适配</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>正向-切换树脂后自动调用预设参数</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>打印机内已存储两种树脂配置：标准树脂（曝光10s）和柔性树脂（曝光15s）</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1. 将树脂槽从标准树脂更换为柔性树脂
+2. 在界面选择“柔性树脂”类型
+3. 观察曝光参数</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>曝光时间自动从10s变为15s，其他相关参数（提升速度、等待时间等）同步更新为柔性树脂配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>树脂参数适配</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>反向-未适配树脂打印导致固化异常</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>树脂槽内装有不支持的非标准树脂（如高粘度树脂）</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1. 不修改任何参数，直接使用标准树脂配置开始打印
+2. 持续监控打印过程
+3. 打印完成后取出模型</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>模型出现层间分离、表面不完整或过度固化，固化异常明显</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>树脂兼容性</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>正向-支持常见标准树脂正常打印</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>树脂槽内装入市售标准光敏树脂（如Anycubic标准树脂）</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1. 加载标准测试模型文件
+2. 调用对应树脂的参数配置
+3. 开始打印</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>打印顺利完成，模型尺寸精度±0.2mm，表面质量良好</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="25" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>树脂兼容性</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>反向-腐蚀性树脂损坏树脂槽</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>准备具有腐蚀性的实验树脂（pH&lt;3或含强溶剂）</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1. 将腐蚀性树脂倒入树脂槽
+2. 静置24小时
+3. 倒出树脂，观察树脂槽内表面</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>树脂槽底部出现腐蚀痕迹、变色或裂纹，密封圈膨胀变形，漏斗测试发现泄漏</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="25" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>App远程连接</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>正向-App成功连接打印机并显示状态</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>打印机已连接WiFi且运行正常，手机已安装最新版App</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1. 打开手机App
+2. 扫描打印机二维码进行绑定
+3. 查看App主界面</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>App界面显示打印机在线，并实时更新打印状态（待机/打印中/暂停）、温度、Z轴位置等信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="25" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>App远程连接</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>反向-WiFi断连后App提示离线</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>打印机与App处于正常连接状态</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1. 关闭打印机连接的WiFi路由器
+2. 等待30秒
+3. 查看App界面</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>App上打印机状态由“在线”变为“离线”，并弹出提示“打印机已断开连接”</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="25" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>App远程控制</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>正向-通过App启动暂停停止打印</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>打印机已连接App，文件已加载，处于待机状态</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1. 在App上点击“开始打印”
+2. 打印第3层时点击“暂停”
+3. 30秒后点击“继续”
+4. 打印第8层时点击“停止”</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>打印机依次响应：启动、暂停、继续、停止，打印机状态在App同步更新，停止后打印任务结束</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="25" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>App远程控制</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>反向-App发送无效指令设备忽略</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>打印机正在正常打印中</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1. 使用App调试接口发送非标准指令（如“JUMP”）
+2. 发送超出范围的参数指令（如设置曝光时间-5s）</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>打印机忽略无效指令，继续当前打印流程，App收到“无效指令”提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="25" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>树脂槽密封性</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>正向-树脂槽装料后无泄漏</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>树脂槽清洁干燥，密封圈完好</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1. 将树脂槽装满标准树脂至最大刻度线
+2. 静置在水平桌面上2小时
+3. 用白色纸巾擦拭树脂槽底部四周及接口处</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>纸巾无树脂痕迹，树脂槽底部及接口干燥无渗漏</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="25" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>树脂槽密封性</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>反向-槽体裂缝导致漏料报警</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>在树脂槽底部人为制作一条细裂缝（0.2mm宽）</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1. 向树脂槽中加入树脂至刻度线
+2. 等待5分钟
+3. 观察打印机是否有漏料检测报警</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>树脂从裂缝缓慢渗出，打印机在检测到树脂液位异常下降或底部传感器触发后，屏幕显示“树脂泄漏，请检查树脂槽”报警</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="25" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>光源系统寿命</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>正向-光源连续工作100小时亮度稳定</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>光源已累计使用50小时，状态正常</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1. 记录当前照度值（参考点）
+2. 使光源连续工作100小时（模拟长时间打印）
+3. 每隔20小时测量一次照度
+4. 比较最终照度与初始照度</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>100小时后照度降低不超过10%（即在初始照度的90%~110%之间），光源无闪烁或色偏</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="25" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>光源系统寿命</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>反向-光源老化后曝光明暗不均</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>使用一个已通知老化的光源（累计使用&gt;5000小时或出现明显亮度衰减）</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1. 运行投影全幅白色画面
+2. 使用照度计测量9点照度
+3. 打印标准测试板</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>9点照度差异&gt;20%，打印出的测试板局部固化厚度差异明显，厚度差&gt;0.3mm</t>
         </is>
       </c>
     </row>
